--- a/McLennan-Community-College/_MCCSVA/Officer Interest Sheet.xlsx
+++ b/McLennan-Community-College/_MCCSVA/Officer Interest Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d62837459e03f1f2/Documents/Github-Repo-for-Schools/McLennan-Community-College/_MCCSVA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_6F4D07011E43C98649FB880530DD7AD9575B09A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{936AE5B6-F6FF-4A11-B193-497051898351}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_6F4D07011E43C98649FB880530DD7AD9575B09A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{101D57EC-78BD-4345-87B3-DCD01F6EA923}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -207,11 +207,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -219,15 +234,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,24 +483,24 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
       <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -801,46 +819,46 @@
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
+      <c r="A50" s="12"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
+      <c r="A52" s="12"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
@@ -893,17 +911,121 @@
     </row>
   </sheetData>
   <mergeCells count="150">
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D15:D16"/>
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="B43:B44"/>
@@ -928,125 +1050,21 @@
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="C45:C46"/>
     <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="65" fitToHeight="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="63" fitToHeight="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;12MCCSVA Officer Interest Sheet&amp;C&amp;12&amp;D</oddHeader>
     <oddFooter>&amp;L&amp;"-,Bold"&amp;14Eligibility Checklist:&amp;"-,Regular"&amp;10
